--- a/tests/fixtures/workbooks/relationships/rel_orphan_and_partial.xlsx
+++ b/tests/fixtures/workbooks/relationships/rel_orphan_and_partial.xlsx
@@ -424,7 +424,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>ParentId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
